--- a/AAII_Financials/Yearly/WYHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WYHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>WYHG</t>
   </si>
@@ -714,10 +714,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>133100</v>
+        <v>135200</v>
       </c>
       <c r="E8" s="3">
-        <v>133300</v>
+        <v>144600</v>
       </c>
       <c r="F8" s="3">
         <v>134100</v>
@@ -747,10 +747,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>94200</v>
+        <v>95700</v>
       </c>
       <c r="E9" s="3">
-        <v>92000</v>
+        <v>99800</v>
       </c>
       <c r="F9" s="3">
         <v>87000</v>
@@ -780,10 +780,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>38900</v>
+        <v>39500</v>
       </c>
       <c r="E10" s="3">
-        <v>41300</v>
+        <v>44800</v>
       </c>
       <c r="F10" s="3">
         <v>47100</v>
@@ -828,10 +828,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>3800</v>
+        <v>4100</v>
       </c>
       <c r="E12" s="3">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="3">
         <v>4300</v>
@@ -893,11 +893,11 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>600</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -927,10 +927,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2300</v>
+        <v>5800</v>
       </c>
       <c r="E15" s="3">
-        <v>1200</v>
+        <v>4500</v>
       </c>
       <c r="F15" s="3">
         <v>3000</v>
@@ -972,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>122800</v>
+        <v>124600</v>
       </c>
       <c r="E17" s="3">
-        <v>119500</v>
+        <v>128900</v>
       </c>
       <c r="F17" s="3">
         <v>114800</v>
@@ -1005,10 +1005,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10300</v>
+        <v>10600</v>
       </c>
       <c r="E18" s="3">
-        <v>13800</v>
+        <v>15800</v>
       </c>
       <c r="F18" s="3">
         <v>19200</v>
@@ -1053,10 +1053,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-500</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="F20" s="3">
         <v>1900</v>
@@ -1086,10 +1086,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13100</v>
+        <v>15900</v>
       </c>
       <c r="E21" s="3">
-        <v>13100</v>
+        <v>17400</v>
       </c>
       <c r="F21" s="3">
         <v>20400</v>
@@ -1119,10 +1119,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E22" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F22" s="3">
         <v>1000</v>
@@ -1152,10 +1152,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8800</v>
+        <v>9100</v>
       </c>
       <c r="E23" s="3">
-        <v>10500</v>
+        <v>12100</v>
       </c>
       <c r="F23" s="3">
         <v>16500</v>
@@ -1185,10 +1185,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E24" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F24" s="3">
         <v>2500</v>
@@ -1251,10 +1251,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="E26" s="3">
-        <v>9700</v>
+        <v>11200</v>
       </c>
       <c r="F26" s="3">
         <v>14000</v>
@@ -1284,10 +1284,10 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="E27" s="3">
-        <v>9700</v>
+        <v>11300</v>
       </c>
       <c r="F27" s="3">
         <v>14000</v>
@@ -1449,10 +1449,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
-        <v>-1900</v>
+        <v>-2800</v>
       </c>
       <c r="F32" s="3">
         <v>-1900</v>
@@ -1482,10 +1482,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="E33" s="3">
-        <v>9700</v>
+        <v>11200</v>
       </c>
       <c r="F33" s="3">
         <v>14000</v>
@@ -1548,10 +1548,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="E35" s="3">
-        <v>9700</v>
+        <v>11200</v>
       </c>
       <c r="F35" s="3">
         <v>14000</v>
@@ -1649,10 +1649,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>84600</v>
+        <v>85300</v>
       </c>
       <c r="E41" s="3">
-        <v>87400</v>
+        <v>87900</v>
       </c>
       <c r="F41" s="3">
         <v>91000</v>
@@ -1685,7 +1685,7 @@
         <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
@@ -1715,10 +1715,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7500</v>
+        <v>6800</v>
       </c>
       <c r="E43" s="3">
-        <v>8600</v>
+        <v>8100</v>
       </c>
       <c r="F43" s="3">
         <v>8400</v>
@@ -1751,7 +1751,7 @@
         <v>9800</v>
       </c>
       <c r="E44" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="F44" s="3">
         <v>6600</v>
@@ -1781,10 +1781,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>29900</v>
+        <v>13200</v>
       </c>
       <c r="E45" s="3">
-        <v>4100</v>
+        <v>2200</v>
       </c>
       <c r="F45" s="3">
         <v>1100</v>
@@ -1814,10 +1814,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>131900</v>
+        <v>132200</v>
       </c>
       <c r="E46" s="3">
-        <v>109400</v>
+        <v>112800</v>
       </c>
       <c r="F46" s="3">
         <v>108800</v>
@@ -1880,10 +1880,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>81900</v>
+        <v>82400</v>
       </c>
       <c r="E48" s="3">
-        <v>82900</v>
+        <v>79900</v>
       </c>
       <c r="F48" s="3">
         <v>70700</v>
@@ -1913,10 +1913,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F49" s="3">
         <v>700</v>
@@ -2078,10 +2078,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>214000</v>
+        <v>215300</v>
       </c>
       <c r="E54" s="3">
-        <v>192500</v>
+        <v>193500</v>
       </c>
       <c r="F54" s="3">
         <v>181000</v>
@@ -2141,10 +2141,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10300</v>
+        <v>10400</v>
       </c>
       <c r="E57" s="3">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="F57" s="3">
         <v>7800</v>
@@ -2174,10 +2174,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14700</v>
+        <v>14800</v>
       </c>
       <c r="E58" s="3">
-        <v>17200</v>
+        <v>17300</v>
       </c>
       <c r="F58" s="3">
         <v>7300</v>
@@ -2207,10 +2207,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>2400</v>
+        <v>700</v>
       </c>
       <c r="F59" s="3">
         <v>1200</v>
@@ -2240,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>28200</v>
+        <v>27700</v>
       </c>
       <c r="E60" s="3">
-        <v>32100</v>
+        <v>31600</v>
       </c>
       <c r="F60" s="3">
         <v>19400</v>
@@ -2273,10 +2273,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13900</v>
+        <v>14000</v>
       </c>
       <c r="E61" s="3">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="F61" s="3">
         <v>16900</v>
@@ -2305,8 +2305,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>10</v>
@@ -2438,10 +2438,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>43800</v>
+        <v>43400</v>
       </c>
       <c r="E66" s="3">
-        <v>38000</v>
+        <v>37700</v>
       </c>
       <c r="F66" s="3">
         <v>38000</v>
@@ -2618,10 +2618,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>125600</v>
+        <v>130000</v>
       </c>
       <c r="E72" s="3">
-        <v>113000</v>
+        <v>122100</v>
       </c>
       <c r="F72" s="3">
         <v>110800</v>
@@ -2750,10 +2750,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>170100</v>
+        <v>171900</v>
       </c>
       <c r="E76" s="3">
-        <v>154600</v>
+        <v>155700</v>
       </c>
       <c r="F76" s="3">
         <v>143100</v>
@@ -2854,10 +2854,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="E81" s="3">
-        <v>9700</v>
+        <v>11200</v>
       </c>
       <c r="F81" s="3">
         <v>14000</v>
@@ -2902,10 +2902,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7400</v>
+        <v>5900</v>
       </c>
       <c r="E83" s="3">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="F83" s="3">
         <v>3200</v>
@@ -3100,10 +3100,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1800</v>
+        <v>-13200</v>
       </c>
       <c r="E89" s="3">
-        <v>14900</v>
+        <v>12500</v>
       </c>
       <c r="F89" s="3">
         <v>17700</v>
@@ -3151,7 +3151,7 @@
         <v>-4500</v>
       </c>
       <c r="E91" s="3">
-        <v>-19200</v>
+        <v>-10100</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
@@ -3247,10 +3247,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15800</v>
+        <v>-4500</v>
       </c>
       <c r="E94" s="3">
-        <v>-20100</v>
+        <v>-10100</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
@@ -3430,7 +3430,7 @@
         <v>7500</v>
       </c>
       <c r="E100" s="3">
-        <v>4700</v>
+        <v>4400</v>
       </c>
       <c r="F100" s="3">
         <v>6100</v>
@@ -3460,10 +3460,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6500</v>
+        <v>-3400</v>
       </c>
       <c r="E102" s="3">
-        <v>-500</v>
+        <v>-2200</v>
       </c>
       <c r="F102" s="3">
         <v>23600</v>
